--- a/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
+++ b/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
@@ -53,25 +53,25 @@
     <t>Indicador de Evaluación</t>
   </si>
   <si>
-    <t>PUNTOS</t>
+    <t>Nota</t>
   </si>
   <si>
-    <t>Nota</t>
+    <t>INTEGRANTES</t>
+  </si>
+  <si>
+    <t>GRUPAL</t>
+  </si>
+  <si>
+    <t>PUNTOS</t>
   </si>
   <si>
     <t>NOTA</t>
   </si>
   <si>
-    <t>INTEGRANTES</t>
+    <t>JORDAN MAURICIO VERGARA CARRASCO</t>
   </si>
   <si>
     <t>Categorías de Respuesta</t>
-  </si>
-  <si>
-    <t>GRUPAL</t>
-  </si>
-  <si>
-    <t>Jordan Vergara</t>
   </si>
   <si>
     <t>Ponderación del Indicador de Evaluación</t>
@@ -120,6 +120,9 @@
     <t xml:space="preserve">Logro incipiente </t>
   </si>
   <si>
+    <t>GIBRAN ETIEL BEIZA MOYA</t>
+  </si>
+  <si>
     <t>No logrado</t>
   </si>
   <si>
@@ -136,9 +139,6 @@
   </si>
   <si>
     <t>No incluye ajustes ni justifica por qué mantiene su plan inicial.</t>
-  </si>
-  <si>
-    <t>Gibran Beiza</t>
   </si>
   <si>
     <t>2. Aplica una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</t>
@@ -171,6 +171,9 @@
     <t>Presenta evidencias de avance sin cumplir con lo planificado por el equipo en relación a documentación, programación y almacenamiento de datos y las evidencias no cumplen con estándares de desarrollo que actualmente se encuentran presentes en la industria</t>
   </si>
   <si>
+    <t>Nivel de Logro</t>
+  </si>
+  <si>
     <t>4. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve">No utiliza lenguaje técnico de su disciplina en los entregables de avance del proyecto. </t>
+  </si>
+  <si>
+    <t>NIVELES DE LOGRO Y PUNTAJES</t>
   </si>
   <si>
     <t xml:space="preserve">5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </t>
@@ -219,6 +225,9 @@
     <t>7.- Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</t>
   </si>
   <si>
+    <t>Aspectos a Evaluar</t>
+  </si>
+  <si>
     <t>Generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante</t>
   </si>
   <si>
@@ -231,6 +240,9 @@
     <t>No generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo por lo que no se permite identificar la equidad en el trabajo y la participación de cada estudiante</t>
   </si>
   <si>
+    <t>Completamente logrado</t>
+  </si>
+  <si>
     <t>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</t>
   </si>
   <si>
@@ -240,25 +252,13 @@
     <t>Demuestra un trabajo en equipo de manera parcial, en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto, pero no todos participan de manera equitativa de las actividades planificadas en el proyecto</t>
   </si>
   <si>
+    <t>Logrado</t>
+  </si>
+  <si>
     <t>Demuestra de manera deficiente el trabajo en equipo en donde los integrantes expresan con poca fluidez y de manera imparcial el conocimiento del tema expuesto y no todos sus miembros participan de manera equitativa de las actividades planificadas en el proyecto</t>
   </si>
   <si>
     <t xml:space="preserve">No demuestran un trabajo en equipo, evidenciando en su presentación la nula colaboración de alguno de sus integrantes. </t>
-  </si>
-  <si>
-    <t>Nivel de Logro</t>
-  </si>
-  <si>
-    <t>NIVELES DE LOGRO Y PUNTAJES</t>
-  </si>
-  <si>
-    <t>Aspectos a Evaluar</t>
-  </si>
-  <si>
-    <t>Completamente logrado</t>
-  </si>
-  <si>
-    <t>Logrado</t>
   </si>
   <si>
     <t>Logro Incipiente</t>
@@ -302,14 +302,14 @@
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font/>
@@ -331,8 +331,14 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="20.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -342,14 +348,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="20.0"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -429,6 +429,17 @@
       </top>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -456,17 +467,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
@@ -514,6 +514,17 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <right style="medium">
         <color rgb="FF7F7F7F"/>
       </right>
@@ -523,17 +534,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
     </border>
     <border>
       <top style="thin">
@@ -683,83 +683,83 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="255" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -769,40 +769,40 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="19" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="20" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="24" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="26" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="14" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
@@ -1076,100 +1076,100 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="C4" s="14">
         <f>EVALUACION2!$C$22</f>
         <v>7</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="9">
+      <c r="A5" s="6">
         <v>2.0</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="14">
         <f>EVALUACION2!$C$22</f>
         <v>7</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="9">
+      <c r="A6" s="6">
         <v>3.0</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="19">
+      <c r="B6" s="18"/>
+      <c r="C6" s="14">
         <f>EVALUACION2!$C$22</f>
         <v>7</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="11" outlineLevel="1">
-      <c r="A11" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="32"/>
+      <c r="A11" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="29"/>
     </row>
     <row r="12" outlineLevel="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="29"/>
+      <c r="F12" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="30" t="s">
+      <c r="G12" s="29"/>
+      <c r="H12" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="32"/>
-      <c r="J12" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="32"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="29"/>
     </row>
     <row r="13" outlineLevel="1">
-      <c r="A13" s="33"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="36" t="str">
         <f>RUBRICA!A4</f>
         <v>1. Propone ajustes al Proyecto APT considerando dificultades, facilitadores y retroalimentación. </v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" s="38" t="str">
         <f>IF($C13=CL,"X","")</f>
@@ -1205,13 +1205,13 @@
       </c>
     </row>
     <row r="14" ht="26.25" customHeight="1" outlineLevel="1">
-      <c r="A14" s="33"/>
+      <c r="A14" s="30"/>
       <c r="B14" s="36" t="str">
         <f>RUBRICA!A5</f>
         <v>2. Aplica una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D14" s="38" t="str">
         <f>IF($C14=CL,"X","")</f>
@@ -1247,13 +1247,13 @@
       </c>
     </row>
     <row r="15" outlineLevel="1">
-      <c r="A15" s="33"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="36" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Genera evidencias que dan cuenta del avance del Proyecto APT en relación a documentación, programación y almacenamiento de datos , de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D15" s="38" t="str">
         <f>IF($C15=CL,"X","")</f>
@@ -1289,13 +1289,13 @@
       </c>
     </row>
     <row r="16" outlineLevel="1">
-      <c r="A16" s="33"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="36" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D16" s="38" t="str">
         <f>IF($C16=CL,"X","")</f>
@@ -1331,13 +1331,13 @@
       </c>
     </row>
     <row r="17" outlineLevel="1">
-      <c r="A17" s="33"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="36" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D17" s="38" t="str">
         <f>IF($C17=CL,"X","")</f>
@@ -1373,13 +1373,13 @@
       </c>
     </row>
     <row r="18" outlineLevel="1">
-      <c r="A18" s="33"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="36" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" s="38" t="str">
         <f>IF($C18=CL,"X","")</f>
@@ -1415,13 +1415,13 @@
       </c>
     </row>
     <row r="19" outlineLevel="1">
-      <c r="A19" s="33"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="36" t="str">
         <f>RUBRICA!A10</f>
         <v>7.- Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D19" s="38" t="str">
         <f>IF($C19=CL,"X","")</f>
@@ -1457,13 +1457,13 @@
       </c>
     </row>
     <row r="20" outlineLevel="1">
-      <c r="A20" s="33"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="36" t="str">
         <f>RUBRICA!A11</f>
         <v>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D20" s="38" t="str">
         <f>IF($C20=CL,"X","")</f>
@@ -1499,7 +1499,7 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A21" s="33"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="49" t="s">
         <v>0</v>
       </c>
@@ -1529,9 +1529,9 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A22" s="35"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="52" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="53">
         <f>VLOOKUP(C21,ESCALA_IEP!A2:B202,2,FALSE)</f>
@@ -2575,16 +2575,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2596,183 +2596,183 @@
       <c r="C2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>13</v>
+      <c r="E2" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="19">
         <v>-0.3</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="19">
         <v>0.0</v>
       </c>
-      <c r="F3" s="18"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="21">
+      <c r="E4" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="22">
         <v>10.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <v>10.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <v>25.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="C7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="21">
+      <c r="E7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="22">
         <v>5.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="22">
+      <c r="D8" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="27">
         <v>5.0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="C9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="21">
+      <c r="D9" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="22">
         <v>20.0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="A10" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="B10" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="25">
+      <c r="C10" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="34">
         <v>15.0</v>
       </c>
     </row>
     <row r="11" ht="81.0" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26">
+      <c r="B11" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="35">
         <v>10.0</v>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -6224,17 +6224,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>0.0</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="7">
         <v>1.0</v>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       <c r="A3" s="1">
         <v>1.0</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="7">
         <v>1.1</v>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       <c r="A4" s="1">
         <v>2.0</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="7">
         <v>1.2</v>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       <c r="A5" s="1">
         <v>3.0</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="7">
         <v>1.3</v>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       <c r="A6" s="1">
         <v>4.0</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="7">
         <v>1.4</v>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       <c r="A7" s="1">
         <v>5.0</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="7">
         <v>1.5</v>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       <c r="A8" s="1">
         <v>6.0</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="7">
         <v>1.6</v>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       <c r="A9" s="1">
         <v>7.0</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="7">
         <v>1.7</v>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       <c r="A10" s="1">
         <v>8.0</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="7">
         <v>1.8</v>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       <c r="A11" s="1">
         <v>9.0</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <v>1.9</v>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="A12" s="1">
         <v>10.0</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="7">
         <v>2.0</v>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       <c r="A13" s="1">
         <v>11.0</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="7">
         <v>2.1</v>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       <c r="A14" s="1">
         <v>12.0</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <v>2.2</v>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       <c r="A15" s="1">
         <v>13.0</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <v>2.3</v>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       <c r="A16" s="1">
         <v>14.0</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="7">
         <v>2.3</v>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="A17" s="1">
         <v>15.0</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="7">
         <v>2.4</v>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       <c r="A18" s="1">
         <v>16.0</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="7">
         <v>2.5</v>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       <c r="A19" s="1">
         <v>17.0</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="7">
         <v>2.6</v>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       <c r="A20" s="1">
         <v>18.0</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="7">
         <v>2.7</v>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       <c r="A21" s="1">
         <v>19.0</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="7">
         <v>2.8</v>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       <c r="A22" s="1">
         <v>20.0</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="7">
         <v>2.9</v>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       <c r="A23" s="1">
         <v>21.0</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="7">
         <v>3.0</v>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       <c r="A24" s="1">
         <v>22.0</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="7">
         <v>3.1</v>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       <c r="A25" s="1">
         <v>23.0</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="7">
         <v>3.2</v>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       <c r="A26" s="1">
         <v>24.0</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="7">
         <v>3.3</v>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       <c r="A27" s="1">
         <v>25.0</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="7">
         <v>3.4</v>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       <c r="A28" s="1">
         <v>26.0</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="7">
         <v>3.5</v>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       <c r="A29" s="1">
         <v>27.0</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="7">
         <v>3.6</v>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       <c r="A30" s="1">
         <v>28.0</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="7">
         <v>3.7</v>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       <c r="A31" s="1">
         <v>29.0</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="7">
         <v>3.8</v>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       <c r="A32" s="1">
         <v>30.0</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="7">
         <v>3.9</v>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       <c r="A33" s="1">
         <v>31.0</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="7">
         <v>4.0</v>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       <c r="A34" s="1">
         <v>32.0</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="7">
         <v>4.1</v>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       <c r="A35" s="1">
         <v>33.0</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="7">
         <v>4.3</v>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       <c r="A36" s="1">
         <v>34.0</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="7">
         <v>4.4</v>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       <c r="A37" s="1">
         <v>35.0</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="7">
         <v>4.5</v>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       <c r="A38" s="1">
         <v>36.0</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="7">
         <v>4.7</v>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       <c r="A39" s="1">
         <v>37.0</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="7">
         <v>4.8</v>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       <c r="A40" s="1">
         <v>38.0</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="7">
         <v>5.0</v>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       <c r="A41" s="1">
         <v>39.0</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="7">
         <v>5.1</v>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       <c r="A42" s="1">
         <v>40.0</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="7">
         <v>5.3</v>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       <c r="A43" s="1">
         <v>41.0</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="7">
         <v>5.4</v>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       <c r="A44" s="1">
         <v>42.0</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="7">
         <v>5.6</v>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       <c r="A45" s="1">
         <v>43.0</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="7">
         <v>5.7</v>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       <c r="A46" s="1">
         <v>44.0</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="7">
         <v>5.8</v>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       <c r="A47" s="1">
         <v>45.0</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="7">
         <v>6.0</v>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="A48" s="1">
         <v>46.0</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="7">
         <v>6.1</v>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       <c r="A49" s="1">
         <v>47.0</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="7">
         <v>6.3</v>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       <c r="A50" s="1">
         <v>48.0</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="7">
         <v>6.4</v>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="A51" s="1">
         <v>49.0</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="7">
         <v>6.6</v>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       <c r="A52" s="1">
         <v>50.0</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="7">
         <v>6.7</v>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       <c r="A53" s="1">
         <v>51.0</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="7">
         <v>6.9</v>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       <c r="A54" s="1">
         <v>52.0</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="7">
         <v>7.0</v>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -8035,10 +8035,10 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="B53" s="5"/>
+      <c r="B53" s="7"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="5"/>
+      <c r="B54" s="7"/>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
@@ -9018,16 +9018,16 @@
     <row r="2">
       <c r="A2" s="43"/>
       <c r="B2" s="44" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>62</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">

--- a/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
+++ b/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
@@ -47,13 +47,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
+    <t>PUNTOS</t>
+  </si>
+  <si>
     <t>Puntaje</t>
   </si>
   <si>
     <t>Indicador de Evaluación</t>
   </si>
   <si>
+    <t>NOTA</t>
+  </si>
+  <si>
     <t>Nota</t>
+  </si>
+  <si>
+    <t>Categorías de Respuesta</t>
   </si>
   <si>
     <t>INTEGRANTES</t>
@@ -62,19 +71,10 @@
     <t>GRUPAL</t>
   </si>
   <si>
-    <t>PUNTOS</t>
-  </si>
-  <si>
-    <t>NOTA</t>
+    <t>Ponderación del Indicador de Evaluación</t>
   </si>
   <si>
     <t>JORDAN MAURICIO VERGARA CARRASCO</t>
-  </si>
-  <si>
-    <t>Categorías de Respuesta</t>
-  </si>
-  <si>
-    <t>Ponderación del Indicador de Evaluación</t>
   </si>
   <si>
     <r>
@@ -120,10 +120,10 @@
     <t xml:space="preserve">Logro incipiente </t>
   </si>
   <si>
-    <t>GIBRAN ETIEL BEIZA MOYA</t>
+    <t>No logrado</t>
   </si>
   <si>
-    <t>No logrado</t>
+    <t>GIBRAN ETIEL BEIZA MOYA</t>
   </si>
   <si>
     <t xml:space="preserve">1. Propone ajustes al Proyecto APT considerando dificultades, facilitadores y retroalimentación. </t>
@@ -171,9 +171,6 @@
     <t>Presenta evidencias de avance sin cumplir con lo planificado por el equipo en relación a documentación, programación y almacenamiento de datos y las evidencias no cumplen con estándares de desarrollo que actualmente se encuentran presentes en la industria</t>
   </si>
   <si>
-    <t>Nivel de Logro</t>
-  </si>
-  <si>
     <t>4. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
   </si>
   <si>
     <t xml:space="preserve">No utiliza lenguaje técnico de su disciplina en los entregables de avance del proyecto. </t>
-  </si>
-  <si>
-    <t>NIVELES DE LOGRO Y PUNTAJES</t>
   </si>
   <si>
     <t xml:space="preserve">5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </t>
@@ -225,9 +219,6 @@
     <t>7.- Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</t>
   </si>
   <si>
-    <t>Aspectos a Evaluar</t>
-  </si>
-  <si>
     <t>Generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante</t>
   </si>
   <si>
@@ -240,7 +231,10 @@
     <t>No generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo por lo que no se permite identificar la equidad en el trabajo y la participación de cada estudiante</t>
   </si>
   <si>
-    <t>Completamente logrado</t>
+    <t>Nivel de Logro</t>
+  </si>
+  <si>
+    <t>NIVELES DE LOGRO Y PUNTAJES</t>
   </si>
   <si>
     <t>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</t>
@@ -252,13 +246,19 @@
     <t>Demuestra un trabajo en equipo de manera parcial, en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto, pero no todos participan de manera equitativa de las actividades planificadas en el proyecto</t>
   </si>
   <si>
-    <t>Logrado</t>
-  </si>
-  <si>
     <t>Demuestra de manera deficiente el trabajo en equipo en donde los integrantes expresan con poca fluidez y de manera imparcial el conocimiento del tema expuesto y no todos sus miembros participan de manera equitativa de las actividades planificadas en el proyecto</t>
   </si>
   <si>
     <t xml:space="preserve">No demuestran un trabajo en equipo, evidenciando en su presentación la nula colaboración de alguno de sus integrantes. </t>
+  </si>
+  <si>
+    <t>Aspectos a Evaluar</t>
+  </si>
+  <si>
+    <t>Completamente logrado</t>
+  </si>
+  <si>
+    <t>Logrado</t>
   </si>
   <si>
     <t>Logro Incipiente</t>
@@ -302,14 +302,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font/>
@@ -336,6 +336,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FF000000"/>
@@ -345,11 +350,6 @@
       <b/>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -372,14 +372,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECECEC"/>
-        <bgColor rgb="FFECECEC"/>
+        <fgColor rgb="FF262626"/>
+        <bgColor rgb="FF262626"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF262626"/>
-        <bgColor rgb="FF262626"/>
+        <fgColor rgb="FFECECEC"/>
+        <bgColor rgb="FFECECEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -429,17 +429,6 @@
       </top>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -467,6 +456,17 @@
       </top>
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
@@ -514,6 +514,17 @@
       </bottom>
     </border>
     <border>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -523,17 +534,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <top style="thin">
@@ -675,52 +675,49 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf borderId="8" fillId="2" fontId="3" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -729,37 +726,40 @@
     <xf borderId="11" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="255" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="17" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -769,40 +769,43 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="19" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="20" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="24" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="26" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="23" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="14" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
@@ -1071,105 +1074,105 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="10">
         <v>1.0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="18">
+        <f>EVALUACION2!$C$22</f>
+        <v>6.6</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="18">
+        <f>EVALUACION2!$C$22</f>
+        <v>6.6</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="18">
+        <f>EVALUACION2!$C$22</f>
+        <v>6.6</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="14">
-        <f>EVALUACION2!$C$22</f>
-        <v>7</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="32"/>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="32"/>
+      <c r="H12" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="32"/>
+      <c r="J12" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="14">
-        <f>EVALUACION2!$C$22</f>
-        <v>7</v>
-      </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="14">
-        <f>EVALUACION2!$C$22</f>
-        <v>7</v>
-      </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="11" outlineLevel="1">
-      <c r="A11" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" outlineLevel="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="29"/>
+      <c r="K12" s="32"/>
     </row>
     <row r="13" outlineLevel="1">
-      <c r="A13" s="30"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="36" t="str">
         <f>RUBRICA!A4</f>
         <v>1. Propone ajustes al Proyecto APT considerando dificultades, facilitadores y retroalimentación. </v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" s="38" t="str">
         <f>IF($C13=CL,"X","")</f>
@@ -1205,13 +1208,13 @@
       </c>
     </row>
     <row r="14" ht="26.25" customHeight="1" outlineLevel="1">
-      <c r="A14" s="30"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="36" t="str">
         <f>RUBRICA!A5</f>
         <v>2. Aplica una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D14" s="38" t="str">
         <f>IF($C14=CL,"X","")</f>
@@ -1247,13 +1250,13 @@
       </c>
     </row>
     <row r="15" outlineLevel="1">
-      <c r="A15" s="30"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="36" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Genera evidencias que dan cuenta del avance del Proyecto APT en relación a documentación, programación y almacenamiento de datos , de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D15" s="38" t="str">
         <f>IF($C15=CL,"X","")</f>
@@ -1289,29 +1292,29 @@
       </c>
     </row>
     <row r="16" outlineLevel="1">
-      <c r="A16" s="30"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="36" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</v>
       </c>
-      <c r="C16" s="37" t="s">
-        <v>53</v>
+      <c r="C16" s="49" t="s">
+        <v>59</v>
       </c>
       <c r="D16" s="38" t="str">
         <f>IF($C16=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E16" s="38">
+        <v/>
+      </c>
+      <c r="E16" s="38" t="str">
         <f t="shared" ref="E16:E17" si="5">IF(D16="X",100*0.05,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F16" s="38" t="str">
         <f>IF($C16=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G16" s="38" t="str">
+        <v>X</v>
+      </c>
+      <c r="G16" s="38">
         <f t="shared" ref="G16:G17" si="6">IF(F16="X",60*0.05,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H16" s="38" t="str">
         <f>IF($C16=ML,"X","")</f>
@@ -1331,13 +1334,13 @@
       </c>
     </row>
     <row r="17" outlineLevel="1">
-      <c r="A17" s="30"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="36" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
       </c>
-      <c r="C17" s="37" t="s">
-        <v>53</v>
+      <c r="C17" s="49" t="s">
+        <v>58</v>
       </c>
       <c r="D17" s="38" t="str">
         <f>IF($C17=CL,"X","")</f>
@@ -1373,13 +1376,13 @@
       </c>
     </row>
     <row r="18" outlineLevel="1">
-      <c r="A18" s="30"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="36" t="str">
         <f>RUBRICA!A9</f>
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D18" s="38" t="str">
         <f>IF($C18=CL,"X","")</f>
@@ -1415,13 +1418,13 @@
       </c>
     </row>
     <row r="19" outlineLevel="1">
-      <c r="A19" s="30"/>
+      <c r="A19" s="33"/>
       <c r="B19" s="36" t="str">
         <f>RUBRICA!A10</f>
         <v>7.- Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</v>
       </c>
-      <c r="C19" s="37" t="s">
-        <v>53</v>
+      <c r="C19" s="49" t="s">
+        <v>58</v>
       </c>
       <c r="D19" s="38" t="str">
         <f>IF($C19=CL,"X","")</f>
@@ -1457,29 +1460,29 @@
       </c>
     </row>
     <row r="20" outlineLevel="1">
-      <c r="A20" s="30"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="36" t="str">
         <f>RUBRICA!A11</f>
         <v>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</v>
       </c>
-      <c r="C20" s="37" t="s">
-        <v>53</v>
+      <c r="C20" s="49" t="s">
+        <v>59</v>
       </c>
       <c r="D20" s="38" t="str">
         <f>IF($C20=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E20" s="38">
+        <v/>
+      </c>
+      <c r="E20" s="38" t="str">
         <f>IF(D20="X",100*0.1,"")</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="F20" s="38" t="str">
         <f>IF($C20=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G20" s="38" t="str">
+        <v>X</v>
+      </c>
+      <c r="G20" s="38">
         <f>IF(F20="X",60*0.1,"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="H20" s="38" t="str">
         <f>IF($C20=ML,"X","")</f>
@@ -1499,43 +1502,43 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A21" s="30"/>
-      <c r="B21" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="50">
+      <c r="A21" s="33"/>
+      <c r="B21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="51">
         <f>E21+G21+I21+K21</f>
-        <v>100</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51">
+        <v>94</v>
+      </c>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52">
         <f>SUM(E13:E20)</f>
-        <v>100</v>
-      </c>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51">
+        <v>85</v>
+      </c>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52">
         <f>SUM(G13:G20)</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51">
+        <v>9</v>
+      </c>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52">
         <f>SUM(I13:I20)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51">
+      <c r="J21" s="52"/>
+      <c r="K21" s="52">
         <f>SUM(K13:K20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A22" s="33"/>
-      <c r="B22" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="53">
+      <c r="A22" s="35"/>
+      <c r="B22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="54">
         <f>VLOOKUP(C21,ESCALA_IEP!A2:B202,2,FALSE)</f>
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1544,14 +1547,14 @@
       </c>
     </row>
     <row r="24" ht="48.0" customHeight="1">
-      <c r="B24" s="54"/>
+      <c r="B24" s="55"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="B25" s="55"/>
-      <c r="C25" s="56"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="57"/>
     </row>
     <row r="26" ht="30.75" customHeight="1">
-      <c r="B26" s="57"/>
+      <c r="B26" s="58"/>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -2575,204 +2578,204 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="5" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="12"/>
+      <c r="A2" s="11"/>
       <c r="B2" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="12"/>
+      <c r="E2" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="19">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17">
         <v>-0.3</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="17">
         <v>0.0</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="21">
         <v>10.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="21">
         <v>10.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>25.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="D7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="F7" s="21">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="22">
+      <c r="B8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="23">
         <v>5.0</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="21" t="s">
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="27">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="E9" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="F9" s="21">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="B10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="22">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="C10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="D10" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="31" t="s">
+      <c r="F10" s="27">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="11" ht="81.0" customHeight="1">
+      <c r="A11" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="34">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="11" ht="81.0" customHeight="1">
-      <c r="A11" s="21" t="s">
+      <c r="B11" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="E11" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="F11" s="30">
         <v>10.0</v>
       </c>
     </row>
@@ -3792,10 +3795,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
@@ -6224,17 +6227,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>0.0</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="2">
         <v>1.0</v>
       </c>
     </row>
@@ -6242,7 +6245,7 @@
       <c r="A3" s="1">
         <v>1.0</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="2">
         <v>1.1</v>
       </c>
     </row>
@@ -6250,7 +6253,7 @@
       <c r="A4" s="1">
         <v>2.0</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="2">
         <v>1.2</v>
       </c>
     </row>
@@ -6258,7 +6261,7 @@
       <c r="A5" s="1">
         <v>3.0</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="2">
         <v>1.3</v>
       </c>
     </row>
@@ -6266,7 +6269,7 @@
       <c r="A6" s="1">
         <v>4.0</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="2">
         <v>1.4</v>
       </c>
     </row>
@@ -6274,7 +6277,7 @@
       <c r="A7" s="1">
         <v>5.0</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="2">
         <v>1.5</v>
       </c>
     </row>
@@ -6282,7 +6285,7 @@
       <c r="A8" s="1">
         <v>6.0</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="2">
         <v>1.6</v>
       </c>
     </row>
@@ -6290,7 +6293,7 @@
       <c r="A9" s="1">
         <v>7.0</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="2">
         <v>1.7</v>
       </c>
     </row>
@@ -6298,7 +6301,7 @@
       <c r="A10" s="1">
         <v>8.0</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="2">
         <v>1.8</v>
       </c>
     </row>
@@ -6306,7 +6309,7 @@
       <c r="A11" s="1">
         <v>9.0</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="2">
         <v>1.9</v>
       </c>
     </row>
@@ -6314,7 +6317,7 @@
       <c r="A12" s="1">
         <v>10.0</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="2">
         <v>2.0</v>
       </c>
     </row>
@@ -6322,7 +6325,7 @@
       <c r="A13" s="1">
         <v>11.0</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="2">
         <v>2.1</v>
       </c>
     </row>
@@ -6330,7 +6333,7 @@
       <c r="A14" s="1">
         <v>12.0</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="2">
         <v>2.2</v>
       </c>
     </row>
@@ -6338,7 +6341,7 @@
       <c r="A15" s="1">
         <v>13.0</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="2">
         <v>2.3</v>
       </c>
     </row>
@@ -6346,7 +6349,7 @@
       <c r="A16" s="1">
         <v>14.0</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="2">
         <v>2.3</v>
       </c>
     </row>
@@ -6354,7 +6357,7 @@
       <c r="A17" s="1">
         <v>15.0</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="2">
         <v>2.4</v>
       </c>
     </row>
@@ -6362,7 +6365,7 @@
       <c r="A18" s="1">
         <v>16.0</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="2">
         <v>2.5</v>
       </c>
     </row>
@@ -6370,7 +6373,7 @@
       <c r="A19" s="1">
         <v>17.0</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="2">
         <v>2.6</v>
       </c>
     </row>
@@ -6378,7 +6381,7 @@
       <c r="A20" s="1">
         <v>18.0</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="2">
         <v>2.7</v>
       </c>
     </row>
@@ -6386,7 +6389,7 @@
       <c r="A21" s="1">
         <v>19.0</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="2">
         <v>2.8</v>
       </c>
     </row>
@@ -6394,7 +6397,7 @@
       <c r="A22" s="1">
         <v>20.0</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="2">
         <v>2.9</v>
       </c>
     </row>
@@ -6402,7 +6405,7 @@
       <c r="A23" s="1">
         <v>21.0</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="2">
         <v>3.0</v>
       </c>
     </row>
@@ -6410,7 +6413,7 @@
       <c r="A24" s="1">
         <v>22.0</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="2">
         <v>3.1</v>
       </c>
     </row>
@@ -6418,7 +6421,7 @@
       <c r="A25" s="1">
         <v>23.0</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="2">
         <v>3.2</v>
       </c>
     </row>
@@ -6426,7 +6429,7 @@
       <c r="A26" s="1">
         <v>24.0</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="2">
         <v>3.3</v>
       </c>
     </row>
@@ -6434,7 +6437,7 @@
       <c r="A27" s="1">
         <v>25.0</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="2">
         <v>3.4</v>
       </c>
     </row>
@@ -6442,7 +6445,7 @@
       <c r="A28" s="1">
         <v>26.0</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="2">
         <v>3.5</v>
       </c>
     </row>
@@ -6450,7 +6453,7 @@
       <c r="A29" s="1">
         <v>27.0</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="2">
         <v>3.6</v>
       </c>
     </row>
@@ -6458,7 +6461,7 @@
       <c r="A30" s="1">
         <v>28.0</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="2">
         <v>3.7</v>
       </c>
     </row>
@@ -6466,7 +6469,7 @@
       <c r="A31" s="1">
         <v>29.0</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="2">
         <v>3.8</v>
       </c>
     </row>
@@ -6474,7 +6477,7 @@
       <c r="A32" s="1">
         <v>30.0</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="2">
         <v>3.9</v>
       </c>
     </row>
@@ -6482,7 +6485,7 @@
       <c r="A33" s="1">
         <v>31.0</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="2">
         <v>4.0</v>
       </c>
     </row>
@@ -6490,7 +6493,7 @@
       <c r="A34" s="1">
         <v>32.0</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="2">
         <v>4.1</v>
       </c>
     </row>
@@ -6498,7 +6501,7 @@
       <c r="A35" s="1">
         <v>33.0</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="2">
         <v>4.3</v>
       </c>
     </row>
@@ -6506,7 +6509,7 @@
       <c r="A36" s="1">
         <v>34.0</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="2">
         <v>4.4</v>
       </c>
     </row>
@@ -6514,7 +6517,7 @@
       <c r="A37" s="1">
         <v>35.0</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="2">
         <v>4.5</v>
       </c>
     </row>
@@ -6522,7 +6525,7 @@
       <c r="A38" s="1">
         <v>36.0</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="2">
         <v>4.7</v>
       </c>
     </row>
@@ -6530,7 +6533,7 @@
       <c r="A39" s="1">
         <v>37.0</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="2">
         <v>4.8</v>
       </c>
     </row>
@@ -6538,7 +6541,7 @@
       <c r="A40" s="1">
         <v>38.0</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="2">
         <v>5.0</v>
       </c>
     </row>
@@ -6546,7 +6549,7 @@
       <c r="A41" s="1">
         <v>39.0</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="2">
         <v>5.1</v>
       </c>
     </row>
@@ -6554,7 +6557,7 @@
       <c r="A42" s="1">
         <v>40.0</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="2">
         <v>5.3</v>
       </c>
     </row>
@@ -6562,7 +6565,7 @@
       <c r="A43" s="1">
         <v>41.0</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="2">
         <v>5.4</v>
       </c>
     </row>
@@ -6570,7 +6573,7 @@
       <c r="A44" s="1">
         <v>42.0</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="2">
         <v>5.6</v>
       </c>
     </row>
@@ -6578,7 +6581,7 @@
       <c r="A45" s="1">
         <v>43.0</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="2">
         <v>5.7</v>
       </c>
     </row>
@@ -6586,7 +6589,7 @@
       <c r="A46" s="1">
         <v>44.0</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="2">
         <v>5.8</v>
       </c>
     </row>
@@ -6594,7 +6597,7 @@
       <c r="A47" s="1">
         <v>45.0</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="2">
         <v>6.0</v>
       </c>
     </row>
@@ -6602,7 +6605,7 @@
       <c r="A48" s="1">
         <v>46.0</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="2">
         <v>6.1</v>
       </c>
     </row>
@@ -6610,7 +6613,7 @@
       <c r="A49" s="1">
         <v>47.0</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="2">
         <v>6.3</v>
       </c>
     </row>
@@ -6618,7 +6621,7 @@
       <c r="A50" s="1">
         <v>48.0</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="2">
         <v>6.4</v>
       </c>
     </row>
@@ -6626,7 +6629,7 @@
       <c r="A51" s="1">
         <v>49.0</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="2">
         <v>6.6</v>
       </c>
     </row>
@@ -6634,7 +6637,7 @@
       <c r="A52" s="1">
         <v>50.0</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="2">
         <v>6.7</v>
       </c>
     </row>
@@ -6642,7 +6645,7 @@
       <c r="A53" s="1">
         <v>51.0</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="2">
         <v>6.9</v>
       </c>
     </row>
@@ -6650,7 +6653,7 @@
       <c r="A54" s="1">
         <v>52.0</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="2">
         <v>7.0</v>
       </c>
     </row>
@@ -7620,10 +7623,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
@@ -8035,10 +8038,10 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="B53" s="7"/>
+      <c r="B53" s="2"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="7"/>
+      <c r="B54" s="2"/>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
@@ -9009,7 +9012,7 @@
         <v>61</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="41"/>
       <c r="D1" s="41"/>
@@ -9018,16 +9021,16 @@
     <row r="2">
       <c r="A2" s="43"/>
       <c r="B2" s="44" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>62</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
